--- a/Result/profitability/2102.xlsx
+++ b/Result/profitability/2102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7349999999999999</v>
+        <v>0.75625</v>
       </c>
       <c r="N2" t="n">
-        <v>15.095</v>
+        <v>16.23875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7775</v>
+        <v>0.81375</v>
       </c>
       <c r="N3" t="n">
-        <v>14.8025</v>
+        <v>18.15875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8312499999999999</v>
+        <v>0.8412499999999998</v>
       </c>
       <c r="N4" t="n">
-        <v>16.755</v>
+        <v>16.93125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.91</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7399999999999999</v>
+        <v>1.00125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.45375</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.015</v>
+        <v>0.9824999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>13.635</v>
+        <v>12.50125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,28 +1264,28 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1125</v>
+        <v>0.03874999999999988</v>
       </c>
       <c r="N7" t="n">
-        <v>12.8525</v>
+        <v>13.095</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1312499999999999</v>
+        <v>0.1174999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>13.25625</v>
+        <v>14.12625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>49</v>
+      </c>
+      <c r="D75" t="n">
+        <v>38</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-87.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-47</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6912499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.83875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.959999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4615384615384615</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.954337899543379</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.279214064115822</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
